--- a/erp-server/erp-server-file/src/main/resources/excel/tms/dictHsCodeExport.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/tms/dictHsCodeExport.xlsx
@@ -46,10 +46,10 @@
     <t>申报要素</t>
   </si>
   <si>
-    <t>{.hsCode}</t>
+    <t>{.description}</t>
   </si>
   <si>
-    <t>{.declareNameCn}</t>
+    <t>{.hsCode}</t>
   </si>
   <si>
     <t>{.exportRebateRate}</t>
